--- a/AVGO.xlsx
+++ b/AVGO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC517A7-4365-43F2-9ED5-146F7B37754D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AAE3F8-6C4C-468B-A45E-2ABBEAB5F07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{04A738BD-2870-4489-8638-5155B260011A}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{04A738BD-2870-4489-8638-5155B260011A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,15 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="63">
   <si>
     <t>Broadcom</t>
   </si>
   <si>
     <t>numbers im mio USD</t>
-  </si>
-  <si>
-    <t>SEC</t>
   </si>
   <si>
     <t>AVGO</t>
@@ -221,6 +218,15 @@
   <si>
     <t>Q426</t>
   </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>Semiconductor Solutions</t>
+  </si>
+  <si>
+    <t>Infrastructure Revenue</t>
+  </si>
 </sst>
 </file>
 
@@ -230,13 +236,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -322,34 +334,35 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -707,10 +720,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="F3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="2">
-        <v>385.02</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -718,7 +731,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="4">
         <v>4757.5801979999997</v>
@@ -728,23 +741,23 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="B5" s="2" t="s">
-        <v>3</v>
+      <c r="B5" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4">
         <f>G3*G4</f>
-        <v>1831763.5278339598</v>
+        <v>1712728.8712799998</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="F6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="4">
-        <v>19628</v>
+        <v>23975</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>58</v>
@@ -752,14 +765,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="B7" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" s="4">
-        <f>2252+62655</f>
-        <v>64907</v>
+        <v>56167</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>58</v>
@@ -767,16 +779,17 @@
     </row>
     <row r="8" spans="1:8">
       <c r="F8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" s="4">
         <f>G5-G6+G7</f>
-        <v>1877042.5278339598</v>
+        <v>1744920.8712799998</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{AEA49E6C-DB34-49AD-93D3-719A199DF624}"/>
+    <hyperlink ref="B4" r:id="rId1" display="SEC" xr:uid="{AEA49E6C-DB34-49AD-93D3-719A199DF624}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{A5B8D9F9-027A-4EEC-B099-C51D57F97C03}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -784,7 +797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{096D1573-7190-410A-B6D0-6D0ABA0DB551}">
-  <dimension ref="A1:CC443"/>
+  <dimension ref="A1:CC445"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="8" customWidth="1"/>
@@ -794,132 +807,109 @@
   <sheetData>
     <row r="1" spans="1:81">
       <c r="A1" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:81">
       <c r="C2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>14</v>
-      </c>
       <c r="G2" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="K2" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="M2" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="N2" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="N2" s="17" t="s">
-        <v>60</v>
-      </c>
       <c r="P2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="R2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="S2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="T2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="U2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="W2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="10" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="3" spans="1:81">
-      <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11">
-        <v>7412</v>
-      </c>
-      <c r="D3" s="11">
-        <v>7192</v>
-      </c>
-      <c r="E3" s="11">
-        <v>7439</v>
-      </c>
+      <c r="B3" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="11">
-        <v>8171</v>
-      </c>
-      <c r="H3" s="11">
-        <v>8506</v>
-      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="11">
-        <v>9257</v>
-      </c>
-      <c r="J3" s="11">
-        <f>+W3-SUM(G3:I3)</f>
-        <v>18913</v>
-      </c>
-      <c r="K3" s="11">
-        <v>14130</v>
-      </c>
-      <c r="L3" s="11">
-        <v>16892</v>
-      </c>
-      <c r="M3" s="11"/>
+        <v>9166</v>
+      </c>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11">
+        <v>20839</v>
+      </c>
       <c r="N3" s="11"/>
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
-      <c r="T3" s="11">
-        <v>26277</v>
-      </c>
-      <c r="U3" s="11">
-        <v>27891</v>
-      </c>
-      <c r="V3" s="11">
-        <v>30359</v>
-      </c>
-      <c r="W3" s="11">
-        <v>44847</v>
-      </c>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
       <c r="X3" s="11"/>
       <c r="Y3" s="11"/>
       <c r="Z3" s="11"/>
@@ -972,65 +962,36 @@
       <c r="BU3" s="11"/>
       <c r="BV3" s="11"/>
       <c r="BW3" s="11"/>
-      <c r="BX3" s="11"/>
-      <c r="BY3" s="11"/>
-      <c r="BZ3" s="11"/>
-      <c r="CA3" s="11"/>
-      <c r="CB3" s="11"/>
-      <c r="CC3" s="11"/>
     </row>
     <row r="4" spans="1:81">
-      <c r="B4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="11">
-        <v>4549</v>
-      </c>
-      <c r="D4" s="11">
-        <v>5295</v>
-      </c>
-      <c r="E4" s="11">
-        <v>5633</v>
-      </c>
+      <c r="B4" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="11">
-        <v>6745</v>
-      </c>
-      <c r="H4" s="11">
-        <v>6498</v>
-      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="11">
-        <v>6695</v>
-      </c>
-      <c r="J4" s="11">
-        <f>+W4-SUM(G4:I4)</f>
-        <v>-898</v>
-      </c>
-      <c r="K4" s="11">
-        <v>4181</v>
-      </c>
-      <c r="L4" s="11">
-        <v>5295</v>
-      </c>
-      <c r="M4" s="11"/>
+        <v>6786</v>
+      </c>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11">
+        <v>8752</v>
+      </c>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
       <c r="R4" s="11"/>
       <c r="S4" s="11"/>
-      <c r="T4" s="11">
-        <v>6926</v>
-      </c>
-      <c r="U4" s="11">
-        <v>7928</v>
-      </c>
-      <c r="V4" s="11">
-        <v>21215</v>
-      </c>
-      <c r="W4" s="11">
-        <v>19040</v>
-      </c>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
       <c r="X4" s="11"/>
       <c r="Y4" s="11"/>
       <c r="Z4" s="11"/>
@@ -1083,77 +1044,58 @@
       <c r="BU4" s="11"/>
       <c r="BV4" s="11"/>
       <c r="BW4" s="11"/>
-      <c r="BX4" s="11"/>
-      <c r="BY4" s="11"/>
-      <c r="BZ4" s="11"/>
-      <c r="CA4" s="11"/>
-      <c r="CB4" s="11"/>
-      <c r="CC4" s="11"/>
     </row>
     <row r="5" spans="1:81">
-      <c r="B5" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="13">
-        <v>11961</v>
-      </c>
-      <c r="D5" s="13">
-        <v>12487</v>
-      </c>
-      <c r="E5" s="13">
-        <f>+E3+E4</f>
-        <v>13072</v>
-      </c>
-      <c r="F5" s="13">
-        <v>14054</v>
-      </c>
-      <c r="G5" s="13">
-        <v>14916</v>
-      </c>
-      <c r="H5" s="13">
-        <v>15004</v>
-      </c>
-      <c r="I5" s="13">
-        <v>15952</v>
-      </c>
-      <c r="J5" s="13">
-        <f>+J3+J4</f>
-        <v>18015</v>
-      </c>
-      <c r="K5" s="13">
-        <v>19311</v>
-      </c>
-      <c r="L5" s="13">
-        <v>22187</v>
-      </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
+      <c r="B5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="11">
+        <v>7412</v>
+      </c>
+      <c r="D5" s="11">
+        <v>7192</v>
+      </c>
+      <c r="E5" s="11">
+        <v>7439</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11">
+        <v>8171</v>
+      </c>
+      <c r="H5" s="11">
+        <v>8506</v>
+      </c>
+      <c r="I5" s="11">
+        <v>9257</v>
+      </c>
+      <c r="J5" s="11">
+        <f>+W5-SUM(G5:I5)</f>
+        <v>18913</v>
+      </c>
+      <c r="K5" s="11">
+        <v>14130</v>
+      </c>
+      <c r="L5" s="11">
+        <v>16892</v>
+      </c>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
-      <c r="R5" s="13">
-        <f t="shared" ref="R5:U5" si="0">SUM(R3:R4)</f>
-        <v>0</v>
-      </c>
-      <c r="S5" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T5" s="13">
-        <f t="shared" si="0"/>
-        <v>33203</v>
-      </c>
-      <c r="U5" s="13">
-        <f t="shared" si="0"/>
-        <v>35819</v>
-      </c>
-      <c r="V5" s="13">
-        <f>SUM(V3:V4)</f>
-        <v>51574</v>
-      </c>
-      <c r="W5" s="13">
-        <f t="shared" ref="W5" si="1">SUM(W3:W4)</f>
-        <v>63887</v>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11">
+        <v>26277</v>
+      </c>
+      <c r="U5" s="11">
+        <v>27891</v>
+      </c>
+      <c r="V5" s="11">
+        <v>30359</v>
+      </c>
+      <c r="W5" s="11">
+        <v>44847</v>
       </c>
       <c r="X5" s="11"/>
       <c r="Y5" s="11"/>
@@ -1216,36 +1158,36 @@
     </row>
     <row r="6" spans="1:81">
       <c r="B6" s="8" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C6" s="11">
-        <v>2160</v>
+        <v>4549</v>
       </c>
       <c r="D6" s="11">
-        <v>2429</v>
+        <v>5295</v>
       </c>
       <c r="E6" s="11">
-        <v>2434</v>
+        <v>5633</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11">
-        <v>2693</v>
+        <v>6745</v>
       </c>
       <c r="H6" s="11">
-        <v>2720</v>
+        <v>6498</v>
       </c>
       <c r="I6" s="11">
-        <v>3096</v>
+        <v>6695</v>
       </c>
       <c r="J6" s="11">
         <f>+W6-SUM(G6:I6)</f>
-        <v>3606</v>
+        <v>-898</v>
       </c>
       <c r="K6" s="11">
-        <v>4041</v>
+        <v>4181</v>
       </c>
       <c r="L6" s="11">
-        <v>4665</v>
+        <v>5295</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
@@ -1255,16 +1197,16 @@
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
       <c r="T6" s="11">
-        <v>7629</v>
+        <v>6926</v>
       </c>
       <c r="U6" s="11">
-        <v>8636</v>
+        <v>7928</v>
       </c>
       <c r="V6" s="11">
-        <v>9797</v>
+        <v>21215</v>
       </c>
       <c r="W6" s="11">
-        <v>12115</v>
+        <v>19040</v>
       </c>
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
@@ -1326,56 +1268,71 @@
       <c r="CC6" s="11"/>
     </row>
     <row r="7" spans="1:81">
-      <c r="B7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="11">
-        <v>954</v>
-      </c>
-      <c r="D7" s="11">
-        <v>713</v>
-      </c>
-      <c r="E7" s="11">
-        <v>699</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11">
-        <v>580</v>
-      </c>
-      <c r="H7" s="11">
-        <v>576</v>
-      </c>
-      <c r="I7" s="11">
-        <v>608</v>
-      </c>
-      <c r="J7" s="11">
-        <f>+W7-SUM(G7:I7)</f>
-        <v>607</v>
-      </c>
-      <c r="K7" s="11">
-        <v>638</v>
-      </c>
-      <c r="L7" s="11">
-        <v>636</v>
-      </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
+      <c r="B7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="13">
+        <v>11961</v>
+      </c>
+      <c r="D7" s="13">
+        <v>12487</v>
+      </c>
+      <c r="E7" s="13">
+        <f>+E5+E6</f>
+        <v>13072</v>
+      </c>
+      <c r="F7" s="13">
+        <v>14054</v>
+      </c>
+      <c r="G7" s="13">
+        <v>14916</v>
+      </c>
+      <c r="H7" s="13">
+        <v>15004</v>
+      </c>
+      <c r="I7" s="13">
+        <v>15952</v>
+      </c>
+      <c r="J7" s="13">
+        <f>+J5+J6</f>
+        <v>18015</v>
+      </c>
+      <c r="K7" s="13">
+        <v>19311</v>
+      </c>
+      <c r="L7" s="13">
+        <v>22187</v>
+      </c>
+      <c r="M7" s="13">
+        <v>29591</v>
+      </c>
+      <c r="N7" s="13"/>
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11">
-        <v>627</v>
-      </c>
-      <c r="U7" s="11">
-        <v>636</v>
-      </c>
-      <c r="V7" s="11">
-        <v>2991</v>
-      </c>
-      <c r="W7" s="11">
-        <v>2371</v>
+      <c r="R7" s="13">
+        <f t="shared" ref="R7:U7" si="0">SUM(R5:R6)</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T7" s="13">
+        <f t="shared" si="0"/>
+        <v>33203</v>
+      </c>
+      <c r="U7" s="13">
+        <f t="shared" si="0"/>
+        <v>35819</v>
+      </c>
+      <c r="V7" s="13">
+        <f>SUM(V5:V6)</f>
+        <v>51574</v>
+      </c>
+      <c r="W7" s="13">
+        <f t="shared" ref="W7" si="1">SUM(W5:W6)</f>
+        <v>63887</v>
       </c>
       <c r="X7" s="11"/>
       <c r="Y7" s="11"/>
@@ -1438,46 +1395,40 @@
     </row>
     <row r="8" spans="1:81">
       <c r="B8" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C8" s="11">
-        <f>1380+92</f>
-        <v>1472</v>
+        <v>2160</v>
       </c>
       <c r="D8" s="11">
-        <f>1516+53</f>
-        <v>1569</v>
+        <v>2429</v>
       </c>
       <c r="E8" s="11">
-        <f>1525+58</f>
-        <v>1583</v>
+        <v>2434</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11">
-        <f>1484+14</f>
-        <v>1498</v>
+        <v>2693</v>
       </c>
       <c r="H8" s="11">
-        <f>1483+28</f>
-        <v>1511</v>
+        <v>2720</v>
       </c>
       <c r="I8" s="11">
-        <f>1519+26</f>
-        <v>1545</v>
+        <v>3096</v>
       </c>
       <c r="J8" s="11">
         <f>+W8-SUM(G8:I8)</f>
-        <v>1553</v>
+        <v>3606</v>
       </c>
       <c r="K8" s="11">
-        <f>1462+13</f>
-        <v>1475</v>
+        <v>4041</v>
       </c>
       <c r="L8" s="11">
-        <f>1461+10</f>
-        <v>1471</v>
-      </c>
-      <c r="M8" s="11"/>
+        <v>4665</v>
+      </c>
+      <c r="M8" s="11">
+        <v>7624</v>
+      </c>
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
@@ -1485,20 +1436,16 @@
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
       <c r="T8" s="11">
-        <f>2847+5</f>
-        <v>2852</v>
+        <v>7629</v>
       </c>
       <c r="U8" s="11">
-        <f>1853+4</f>
-        <v>1857</v>
+        <v>8636</v>
       </c>
       <c r="V8" s="11">
-        <f>6023+254</f>
-        <v>6277</v>
+        <v>9797</v>
       </c>
       <c r="W8" s="11">
-        <f>6031+76</f>
-        <v>6107</v>
+        <v>12115</v>
       </c>
       <c r="X8" s="11"/>
       <c r="Y8" s="11"/>
@@ -1561,82 +1508,57 @@
     </row>
     <row r="9" spans="1:81">
       <c r="B9" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" s="11">
-        <f t="shared" ref="C9:L9" si="2">+C5-SUM(C6:C8)</f>
-        <v>7375</v>
+        <v>954</v>
       </c>
       <c r="D9" s="11">
-        <f t="shared" si="2"/>
-        <v>7776</v>
+        <v>713</v>
       </c>
       <c r="E9" s="11">
-        <f t="shared" si="2"/>
-        <v>8356</v>
-      </c>
-      <c r="F9" s="11">
-        <f t="shared" si="2"/>
-        <v>14054</v>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="F9" s="11"/>
       <c r="G9" s="11">
-        <f t="shared" si="2"/>
-        <v>10145</v>
+        <v>580</v>
       </c>
       <c r="H9" s="11">
-        <f t="shared" si="2"/>
-        <v>10197</v>
+        <v>576</v>
       </c>
       <c r="I9" s="11">
-        <f t="shared" si="2"/>
-        <v>10703</v>
+        <v>608</v>
       </c>
       <c r="J9" s="11">
-        <f t="shared" si="2"/>
-        <v>12249</v>
+        <f>+W9-SUM(G9:I9)</f>
+        <v>607</v>
       </c>
       <c r="K9" s="11">
-        <f t="shared" si="2"/>
-        <v>13157</v>
+        <v>638</v>
       </c>
       <c r="L9" s="11">
-        <f t="shared" si="2"/>
-        <v>15415</v>
-      </c>
-      <c r="M9" s="11"/>
+        <v>636</v>
+      </c>
+      <c r="M9" s="11">
+        <v>1499</v>
+      </c>
       <c r="N9" s="11"/>
       <c r="O9" s="11"/>
-      <c r="P9" s="11">
-        <f t="shared" ref="P9:U9" si="3">+P5-SUM(P6:P8)</f>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
       <c r="T9" s="11">
-        <f t="shared" si="3"/>
-        <v>22095</v>
+        <v>627</v>
       </c>
       <c r="U9" s="11">
-        <f t="shared" si="3"/>
-        <v>24690</v>
+        <v>636</v>
       </c>
       <c r="V9" s="11">
-        <f>+V5-SUM(V6:V8)</f>
-        <v>32509</v>
+        <v>2991</v>
       </c>
       <c r="W9" s="11">
-        <f>+W5-SUM(W6:W8)</f>
-        <v>43294</v>
+        <v>2371</v>
       </c>
       <c r="X9" s="11"/>
       <c r="Y9" s="11"/>
@@ -1699,38 +1621,48 @@
     </row>
     <row r="10" spans="1:81">
       <c r="B10" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C10" s="11">
-        <v>2308</v>
+        <f>1380+92</f>
+        <v>1472</v>
       </c>
       <c r="D10" s="11">
-        <v>2415</v>
+        <f>1516+53</f>
+        <v>1569</v>
       </c>
       <c r="E10" s="11">
-        <v>2353</v>
+        <f>1525+58</f>
+        <v>1583</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11">
-        <v>2253</v>
+        <f>1484+14</f>
+        <v>1498</v>
       </c>
       <c r="H10" s="11">
-        <v>2693</v>
+        <f>1483+28</f>
+        <v>1511</v>
       </c>
       <c r="I10" s="11">
-        <v>3050</v>
+        <f>1519+26</f>
+        <v>1545</v>
       </c>
       <c r="J10" s="11">
         <f>+W10-SUM(G10:I10)</f>
-        <v>2981</v>
+        <v>1553</v>
       </c>
       <c r="K10" s="11">
-        <v>2965</v>
+        <f>1462+13</f>
+        <v>1475</v>
       </c>
       <c r="L10" s="11">
-        <v>2995</v>
-      </c>
-      <c r="M10" s="11"/>
+        <f>1461+10</f>
+        <v>1471</v>
+      </c>
+      <c r="M10" s="11">
+        <v>12</v>
+      </c>
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
@@ -1738,16 +1670,20 @@
       <c r="R10" s="11"/>
       <c r="S10" s="11"/>
       <c r="T10" s="11">
-        <v>4919</v>
+        <f>2847+5</f>
+        <v>2852</v>
       </c>
       <c r="U10" s="11">
-        <v>5253</v>
+        <f>1853+4</f>
+        <v>1857</v>
       </c>
       <c r="V10" s="11">
-        <v>9310</v>
+        <f>6023+254</f>
+        <v>6277</v>
       </c>
       <c r="W10" s="11">
-        <v>10977</v>
+        <f>6031+76</f>
+        <v>6107</v>
       </c>
       <c r="X10" s="11"/>
       <c r="Y10" s="11"/>
@@ -1810,55 +1746,85 @@
     </row>
     <row r="11" spans="1:81">
       <c r="B11" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C11" s="11">
-        <v>1572</v>
+        <f t="shared" ref="C11:M11" si="2">+C7-SUM(C8:C10)</f>
+        <v>7375</v>
       </c>
       <c r="D11" s="11">
-        <v>1277</v>
+        <f t="shared" si="2"/>
+        <v>7776</v>
       </c>
       <c r="E11" s="11">
-        <v>1100</v>
-      </c>
-      <c r="F11" s="11"/>
+        <f t="shared" si="2"/>
+        <v>8356</v>
+      </c>
+      <c r="F11" s="11">
+        <f t="shared" si="2"/>
+        <v>14054</v>
+      </c>
       <c r="G11" s="11">
-        <v>949</v>
+        <f t="shared" si="2"/>
+        <v>10145</v>
       </c>
       <c r="H11" s="11">
-        <v>1083</v>
+        <f t="shared" si="2"/>
+        <v>10197</v>
       </c>
       <c r="I11" s="11">
-        <v>1072</v>
+        <f t="shared" si="2"/>
+        <v>10703</v>
       </c>
       <c r="J11" s="11">
-        <f>+W11-SUM(G11:I11)</f>
-        <v>1107</v>
+        <f t="shared" si="2"/>
+        <v>12249</v>
       </c>
       <c r="K11" s="11">
-        <v>1019</v>
+        <f t="shared" si="2"/>
+        <v>13157</v>
       </c>
       <c r="L11" s="11">
-        <v>1055</v>
-      </c>
-      <c r="M11" s="11"/>
+        <f t="shared" si="2"/>
+        <v>15415</v>
+      </c>
+      <c r="M11" s="11">
+        <f t="shared" si="2"/>
+        <v>20456</v>
+      </c>
       <c r="N11" s="11"/>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
+      <c r="P11" s="11">
+        <f t="shared" ref="P11:U11" si="3">+P7-SUM(P8:P10)</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="T11" s="11">
-        <v>1382</v>
+        <f t="shared" si="3"/>
+        <v>22095</v>
       </c>
       <c r="U11" s="11">
-        <v>1592</v>
+        <f t="shared" si="3"/>
+        <v>24690</v>
       </c>
       <c r="V11" s="11">
-        <v>4959</v>
+        <f>+V7-SUM(V8:V10)</f>
+        <v>32509</v>
       </c>
       <c r="W11" s="11">
-        <v>4211</v>
+        <f>+W7-SUM(W8:W10)</f>
+        <v>43294</v>
       </c>
       <c r="X11" s="11"/>
       <c r="Y11" s="11"/>
@@ -1921,38 +1887,40 @@
     </row>
     <row r="12" spans="1:81">
       <c r="B12" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" s="11">
-        <v>792</v>
+        <v>2308</v>
       </c>
       <c r="D12" s="11">
-        <v>827</v>
+        <v>2415</v>
       </c>
       <c r="E12" s="11">
-        <v>812</v>
+        <v>2353</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11">
-        <v>511</v>
+        <v>2253</v>
       </c>
       <c r="H12" s="11">
-        <v>506</v>
+        <v>2693</v>
       </c>
       <c r="I12" s="11">
-        <v>507</v>
+        <v>3050</v>
       </c>
       <c r="J12" s="11">
         <f>+W12-SUM(G12:I12)</f>
-        <v>507</v>
+        <v>2981</v>
       </c>
       <c r="K12" s="11">
-        <v>507</v>
+        <v>2965</v>
       </c>
       <c r="L12" s="11">
-        <v>506</v>
-      </c>
-      <c r="M12" s="11"/>
+        <v>2995</v>
+      </c>
+      <c r="M12" s="11">
+        <v>2895</v>
+      </c>
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -1960,16 +1928,16 @@
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
       <c r="T12" s="11">
-        <v>1512</v>
+        <v>4919</v>
       </c>
       <c r="U12" s="11">
-        <v>1394</v>
+        <v>5253</v>
       </c>
       <c r="V12" s="11">
-        <v>3244</v>
+        <v>9310</v>
       </c>
       <c r="W12" s="11">
-        <v>2031</v>
+        <v>10977</v>
       </c>
       <c r="X12" s="11"/>
       <c r="Y12" s="11"/>
@@ -2032,38 +2000,40 @@
     </row>
     <row r="13" spans="1:81">
       <c r="B13" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C13" s="11">
-        <v>620</v>
+        <v>1572</v>
       </c>
       <c r="D13" s="11">
-        <v>292</v>
+        <v>1277</v>
       </c>
       <c r="E13" s="11">
-        <v>303</v>
+        <v>1100</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11">
-        <v>172</v>
+        <v>949</v>
       </c>
       <c r="H13" s="11">
-        <v>86</v>
+        <v>1083</v>
       </c>
       <c r="I13" s="11">
-        <v>187</v>
+        <v>1072</v>
       </c>
       <c r="J13" s="11">
         <f>+W13-SUM(G13:I13)</f>
-        <v>146</v>
+        <v>1107</v>
       </c>
       <c r="K13" s="11">
-        <v>103</v>
+        <v>1019</v>
       </c>
       <c r="L13" s="11">
-        <v>71</v>
-      </c>
-      <c r="M13" s="11"/>
+        <v>1055</v>
+      </c>
+      <c r="M13" s="11">
+        <v>996</v>
+      </c>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -2071,16 +2041,16 @@
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
       <c r="T13" s="11">
-        <v>57</v>
+        <v>1382</v>
       </c>
       <c r="U13" s="11">
-        <v>244</v>
+        <v>1592</v>
       </c>
       <c r="V13" s="11">
-        <v>1533</v>
+        <v>4959</v>
       </c>
       <c r="W13" s="11">
-        <v>591</v>
+        <v>4211</v>
       </c>
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
@@ -2143,82 +2113,57 @@
     </row>
     <row r="14" spans="1:81">
       <c r="B14" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C14" s="11">
-        <f t="shared" ref="C14:L14" si="4">+C9-SUM(C10:C13)</f>
-        <v>2083</v>
+        <v>792</v>
       </c>
       <c r="D14" s="11">
-        <f t="shared" si="4"/>
-        <v>2965</v>
+        <v>827</v>
       </c>
       <c r="E14" s="11">
-        <f t="shared" si="4"/>
-        <v>3788</v>
-      </c>
-      <c r="F14" s="11">
-        <f t="shared" si="4"/>
-        <v>14054</v>
-      </c>
+        <v>812</v>
+      </c>
+      <c r="F14" s="11"/>
       <c r="G14" s="11">
-        <f t="shared" si="4"/>
-        <v>6260</v>
+        <v>511</v>
       </c>
       <c r="H14" s="11">
-        <f t="shared" si="4"/>
-        <v>5829</v>
+        <v>506</v>
       </c>
       <c r="I14" s="11">
-        <f t="shared" si="4"/>
-        <v>5887</v>
+        <v>507</v>
       </c>
       <c r="J14" s="11">
-        <f t="shared" si="4"/>
-        <v>7508</v>
+        <f>+W14-SUM(G14:I14)</f>
+        <v>507</v>
       </c>
       <c r="K14" s="11">
-        <f t="shared" si="4"/>
-        <v>8563</v>
+        <v>507</v>
       </c>
       <c r="L14" s="11">
-        <f t="shared" si="4"/>
-        <v>10788</v>
-      </c>
-      <c r="M14" s="11"/>
+        <v>506</v>
+      </c>
+      <c r="M14" s="11">
+        <v>507</v>
+      </c>
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
-      <c r="P14" s="11">
-        <f t="shared" ref="P14:U14" si="5">+P9-SUM(P10:P13)</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
       <c r="T14" s="11">
-        <f t="shared" si="5"/>
-        <v>14225</v>
+        <v>1512</v>
       </c>
       <c r="U14" s="11">
-        <f t="shared" si="5"/>
-        <v>16207</v>
+        <v>1394</v>
       </c>
       <c r="V14" s="11">
-        <f>+V9-SUM(V10:V13)</f>
-        <v>13463</v>
+        <v>3244</v>
       </c>
       <c r="W14" s="11">
-        <f t="shared" ref="W14" si="6">+W9-SUM(W10:W13)</f>
-        <v>25484</v>
+        <v>2031</v>
       </c>
       <c r="X14" s="11"/>
       <c r="Y14" s="11"/>
@@ -2281,40 +2226,40 @@
     </row>
     <row r="15" spans="1:81">
       <c r="B15" s="8" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C15" s="11">
-        <f>-926+185</f>
-        <v>-741</v>
+        <v>620</v>
       </c>
       <c r="D15" s="11">
-        <v>-1047</v>
+        <v>292</v>
       </c>
       <c r="E15" s="11">
-        <v>-1064</v>
+        <v>303</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11">
-        <f>-873+103</f>
-        <v>-770</v>
+        <v>172</v>
       </c>
       <c r="H15" s="11">
-        <v>-769</v>
+        <v>86</v>
       </c>
       <c r="I15" s="11">
-        <v>-807</v>
+        <v>187</v>
       </c>
       <c r="J15" s="11">
         <f>+W15-SUM(G15:I15)</f>
-        <v>-864</v>
+        <v>146</v>
       </c>
       <c r="K15" s="11">
-        <v>-801</v>
+        <v>103</v>
       </c>
       <c r="L15" s="11">
-        <v>-776</v>
-      </c>
-      <c r="M15" s="11"/>
+        <v>71</v>
+      </c>
+      <c r="M15" s="11">
+        <v>103</v>
+      </c>
       <c r="N15" s="11"/>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -2322,16 +2267,16 @@
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
       <c r="T15" s="11">
-        <v>-1737</v>
+        <v>57</v>
       </c>
       <c r="U15" s="11">
-        <v>-1622</v>
+        <v>244</v>
       </c>
       <c r="V15" s="11">
-        <v>-3953</v>
+        <v>1533</v>
       </c>
       <c r="W15" s="11">
-        <v>-3210</v>
+        <v>591</v>
       </c>
       <c r="X15" s="11"/>
       <c r="Y15" s="11"/>
@@ -2394,55 +2339,85 @@
     </row>
     <row r="16" spans="1:81">
       <c r="B16" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C16" s="11">
-        <v>51</v>
+        <f t="shared" ref="C16:M16" si="4">+C11-SUM(C12:C15)</f>
+        <v>2083</v>
       </c>
       <c r="D16" s="11">
-        <v>87</v>
+        <f t="shared" si="4"/>
+        <v>2965</v>
       </c>
       <c r="E16" s="11">
-        <v>82</v>
-      </c>
-      <c r="F16" s="11"/>
+        <f t="shared" si="4"/>
+        <v>3788</v>
+      </c>
+      <c r="F16" s="11">
+        <f t="shared" si="4"/>
+        <v>14054</v>
+      </c>
       <c r="G16" s="11">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>6260</v>
       </c>
       <c r="H16" s="11">
-        <v>25</v>
+        <f t="shared" si="4"/>
+        <v>5829</v>
       </c>
       <c r="I16" s="11">
-        <v>205</v>
+        <f t="shared" si="4"/>
+        <v>5887</v>
       </c>
       <c r="J16" s="11">
-        <f>+W16-SUM(G16:I16)</f>
-        <v>225</v>
+        <f t="shared" si="4"/>
+        <v>7508</v>
       </c>
       <c r="K16" s="11">
-        <v>433</v>
+        <f t="shared" si="4"/>
+        <v>8563</v>
       </c>
       <c r="L16" s="11">
-        <v>118</v>
-      </c>
-      <c r="M16" s="11"/>
+        <f t="shared" si="4"/>
+        <v>10788</v>
+      </c>
+      <c r="M16" s="11">
+        <f t="shared" si="4"/>
+        <v>15955</v>
+      </c>
       <c r="N16" s="11"/>
       <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
+      <c r="P16" s="11">
+        <f t="shared" ref="P16:U16" si="5">+P11-SUM(P12:P15)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="T16" s="11">
-        <v>-54</v>
+        <f t="shared" si="5"/>
+        <v>14225</v>
       </c>
       <c r="U16" s="11">
-        <v>512</v>
+        <f t="shared" si="5"/>
+        <v>16207</v>
       </c>
       <c r="V16" s="11">
-        <v>406</v>
+        <f>+V11-SUM(V12:V15)</f>
+        <v>13463</v>
       </c>
       <c r="W16" s="11">
-        <v>455</v>
+        <f t="shared" ref="W16" si="6">+W11-SUM(W12:W15)</f>
+        <v>25484</v>
       </c>
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
@@ -2505,82 +2480,59 @@
     </row>
     <row r="17" spans="2:81">
       <c r="B17" s="8" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C17" s="11">
-        <f t="shared" ref="C17:L17" si="7">+C14+SUM(C15:C16)</f>
-        <v>1393</v>
+        <f>-926+185</f>
+        <v>-741</v>
       </c>
       <c r="D17" s="11">
-        <f t="shared" si="7"/>
-        <v>2005</v>
+        <v>-1047</v>
       </c>
       <c r="E17" s="11">
-        <f t="shared" si="7"/>
-        <v>2806</v>
-      </c>
-      <c r="F17" s="11">
-        <f t="shared" si="7"/>
-        <v>14054</v>
-      </c>
+        <v>-1064</v>
+      </c>
+      <c r="F17" s="11"/>
       <c r="G17" s="11">
-        <f t="shared" si="7"/>
-        <v>5490</v>
+        <f>-873+103</f>
+        <v>-770</v>
       </c>
       <c r="H17" s="11">
-        <f t="shared" si="7"/>
-        <v>5085</v>
+        <v>-769</v>
       </c>
       <c r="I17" s="11">
-        <f t="shared" si="7"/>
-        <v>5285</v>
+        <v>-807</v>
       </c>
       <c r="J17" s="11">
-        <f t="shared" si="7"/>
-        <v>6869</v>
+        <f>+W17-SUM(G17:I17)</f>
+        <v>-864</v>
       </c>
       <c r="K17" s="11">
-        <f t="shared" si="7"/>
-        <v>8195</v>
+        <v>-801</v>
       </c>
       <c r="L17" s="11">
-        <f t="shared" si="7"/>
-        <v>10130</v>
-      </c>
-      <c r="M17" s="11"/>
+        <v>-776</v>
+      </c>
+      <c r="M17" s="11">
+        <v>-778</v>
+      </c>
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
-      <c r="P17" s="11">
-        <f t="shared" ref="P17:U17" si="8">+P14+SUM(P15:P16)</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="11">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="11">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="11">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
       <c r="T17" s="11">
-        <f t="shared" si="8"/>
-        <v>12434</v>
+        <v>-1737</v>
       </c>
       <c r="U17" s="11">
-        <f t="shared" si="8"/>
-        <v>15097</v>
+        <v>-1622</v>
       </c>
       <c r="V17" s="11">
-        <f>+V14+SUM(V15:V16)</f>
-        <v>9916</v>
+        <v>-3953</v>
       </c>
       <c r="W17" s="11">
-        <f t="shared" ref="W17" si="9">+W14+SUM(W15:W16)</f>
-        <v>22729</v>
+        <v>-3210</v>
       </c>
       <c r="X17" s="11"/>
       <c r="Y17" s="11"/>
@@ -2643,38 +2595,40 @@
     </row>
     <row r="18" spans="2:81">
       <c r="B18" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C18" s="11">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D18" s="11">
-        <v>-116</v>
+        <v>87</v>
       </c>
       <c r="E18" s="11">
-        <v>4238</v>
+        <v>82</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="H18" s="11">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="I18" s="11">
-        <v>1145</v>
+        <v>205</v>
       </c>
       <c r="J18" s="11">
         <f>+W18-SUM(G18:I18)</f>
-        <v>-1649</v>
+        <v>225</v>
       </c>
       <c r="K18" s="11">
-        <v>846</v>
+        <v>433</v>
       </c>
       <c r="L18" s="11">
-        <v>820</v>
-      </c>
-      <c r="M18" s="11"/>
+        <v>118</v>
+      </c>
+      <c r="M18" s="11">
+        <v>98</v>
+      </c>
       <c r="N18" s="11"/>
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
@@ -2682,16 +2636,16 @@
       <c r="R18" s="11"/>
       <c r="S18" s="11"/>
       <c r="T18" s="11">
-        <v>939</v>
+        <v>-54</v>
       </c>
       <c r="U18" s="11">
-        <v>1015</v>
+        <v>512</v>
       </c>
       <c r="V18" s="11">
-        <v>3748</v>
+        <v>406</v>
       </c>
       <c r="W18" s="11">
-        <v>-397</v>
+        <v>455</v>
       </c>
       <c r="X18" s="11"/>
       <c r="Y18" s="11"/>
@@ -2754,82 +2708,85 @@
     </row>
     <row r="19" spans="2:81">
       <c r="B19" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C19" s="11">
-        <f t="shared" ref="C19:L19" si="10">+C17-C18</f>
-        <v>1325</v>
+        <f t="shared" ref="C19:M19" si="7">+C16+SUM(C17:C18)</f>
+        <v>1393</v>
       </c>
       <c r="D19" s="11">
-        <f t="shared" si="10"/>
-        <v>2121</v>
+        <f t="shared" si="7"/>
+        <v>2005</v>
       </c>
       <c r="E19" s="11">
-        <f t="shared" si="10"/>
-        <v>-1432</v>
+        <f t="shared" si="7"/>
+        <v>2806</v>
       </c>
       <c r="F19" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>14054</v>
       </c>
       <c r="G19" s="11">
-        <f t="shared" si="10"/>
-        <v>5503</v>
+        <f t="shared" si="7"/>
+        <v>5490</v>
       </c>
       <c r="H19" s="11">
-        <f t="shared" si="10"/>
-        <v>4965</v>
+        <f t="shared" si="7"/>
+        <v>5085</v>
       </c>
       <c r="I19" s="11">
-        <f t="shared" si="10"/>
-        <v>4140</v>
+        <f t="shared" si="7"/>
+        <v>5285</v>
       </c>
       <c r="J19" s="11">
-        <f t="shared" si="10"/>
-        <v>8518</v>
+        <f t="shared" si="7"/>
+        <v>6869</v>
       </c>
       <c r="K19" s="11">
-        <f t="shared" si="10"/>
-        <v>7349</v>
+        <f t="shared" si="7"/>
+        <v>8195</v>
       </c>
       <c r="L19" s="11">
-        <f t="shared" si="10"/>
-        <v>9310</v>
-      </c>
-      <c r="M19" s="11"/>
+        <f t="shared" si="7"/>
+        <v>10130</v>
+      </c>
+      <c r="M19" s="11">
+        <f t="shared" si="7"/>
+        <v>15275</v>
+      </c>
       <c r="N19" s="11"/>
       <c r="O19" s="11"/>
       <c r="P19" s="11">
-        <f t="shared" ref="P19:U19" si="11">+P17-P18</f>
+        <f t="shared" ref="P19:U19" si="8">+P16+SUM(P17:P18)</f>
         <v>0</v>
       </c>
       <c r="Q19" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R19" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S19" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T19" s="11">
-        <f t="shared" si="11"/>
-        <v>11495</v>
+        <f t="shared" si="8"/>
+        <v>12434</v>
       </c>
       <c r="U19" s="11">
-        <f t="shared" si="11"/>
-        <v>14082</v>
+        <f t="shared" si="8"/>
+        <v>15097</v>
       </c>
       <c r="V19" s="11">
-        <f>+V17-V18</f>
-        <v>6168</v>
+        <f>+V16+SUM(V17:V18)</f>
+        <v>9916</v>
       </c>
       <c r="W19" s="11">
-        <f t="shared" ref="W19" si="12">+W17-W18</f>
-        <v>23126</v>
+        <f t="shared" ref="W19" si="9">+W16+SUM(W17:W18)</f>
+        <v>22729</v>
       </c>
       <c r="X19" s="11"/>
       <c r="Y19" s="11"/>
@@ -2892,38 +2849,40 @@
     </row>
     <row r="20" spans="2:81">
       <c r="B20" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C20" s="11">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D20" s="11">
-        <v>0</v>
+        <v>-116</v>
       </c>
       <c r="E20" s="11">
-        <v>443</v>
+        <v>4238</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="H20" s="11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I20" s="11">
-        <v>0</v>
+        <v>1145</v>
       </c>
       <c r="J20" s="11">
         <f>+W20-SUM(G20:I20)</f>
-        <v>0</v>
+        <v>-1649</v>
       </c>
       <c r="K20" s="11">
-        <v>0</v>
+        <v>846</v>
       </c>
       <c r="L20" s="11">
-        <v>0</v>
-      </c>
-      <c r="M20" s="11"/>
+        <v>820</v>
+      </c>
+      <c r="M20" s="11">
+        <v>2187</v>
+      </c>
       <c r="N20" s="11"/>
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
@@ -2931,16 +2890,16 @@
       <c r="R20" s="11"/>
       <c r="S20" s="11"/>
       <c r="T20" s="11">
-        <v>272</v>
+        <v>939</v>
       </c>
       <c r="U20" s="11">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="V20" s="11">
-        <v>273</v>
+        <v>3748</v>
       </c>
       <c r="W20" s="11">
-        <v>0</v>
+        <v>-397</v>
       </c>
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
@@ -3003,81 +2962,84 @@
     </row>
     <row r="21" spans="2:81">
       <c r="B21" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C21" s="11">
-        <f t="shared" ref="C21:F21" si="13">+C19-C20</f>
+        <f t="shared" ref="C21:M21" si="10">+C19-C20</f>
         <v>1325</v>
       </c>
       <c r="D21" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>2121</v>
       </c>
       <c r="E21" s="11">
-        <f t="shared" si="13"/>
-        <v>-1875</v>
+        <f t="shared" si="10"/>
+        <v>-1432</v>
       </c>
       <c r="F21" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>14054</v>
       </c>
       <c r="G21" s="11">
-        <f>+G19-G20</f>
+        <f t="shared" si="10"/>
         <v>5503</v>
       </c>
       <c r="H21" s="11">
-        <f t="shared" ref="H21:L21" si="14">+H19-H20</f>
+        <f t="shared" si="10"/>
         <v>4965</v>
       </c>
       <c r="I21" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>4140</v>
       </c>
       <c r="J21" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>8518</v>
       </c>
       <c r="K21" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>7349</v>
       </c>
       <c r="L21" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>9310</v>
       </c>
-      <c r="M21" s="11"/>
+      <c r="M21" s="11">
+        <f t="shared" si="10"/>
+        <v>13088</v>
+      </c>
       <c r="N21" s="11"/>
       <c r="O21" s="11"/>
       <c r="P21" s="11">
-        <f t="shared" ref="P21:U21" si="15">+P19-P20</f>
+        <f t="shared" ref="P21:U21" si="11">+P19-P20</f>
         <v>0</v>
       </c>
       <c r="Q21" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R21" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="S21" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T21" s="11">
-        <f t="shared" si="15"/>
-        <v>11223</v>
+        <f t="shared" si="11"/>
+        <v>11495</v>
       </c>
       <c r="U21" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>14082</v>
       </c>
       <c r="V21" s="11">
         <f>+V19-V20</f>
-        <v>5895</v>
+        <v>6168</v>
       </c>
       <c r="W21" s="11">
-        <f t="shared" ref="W21" si="16">+W19-W20</f>
+        <f t="shared" ref="W21" si="12">+W19-W20</f>
         <v>23126</v>
       </c>
       <c r="X21" s="11"/>
@@ -3140,27 +3102,59 @@
       <c r="CC21" s="11"/>
     </row>
     <row r="22" spans="2:81">
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
+      <c r="B22" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="11">
+        <v>0</v>
+      </c>
+      <c r="D22" s="11">
+        <v>0</v>
+      </c>
+      <c r="E22" s="11">
+        <v>443</v>
+      </c>
       <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
+      <c r="G22" s="11">
+        <v>0</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0</v>
+      </c>
+      <c r="J22" s="11">
+        <f>+W22-SUM(G22:I22)</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="11">
+        <v>0</v>
+      </c>
+      <c r="L22" s="11">
+        <v>0</v>
+      </c>
+      <c r="M22" s="11">
+        <v>0</v>
+      </c>
       <c r="N22" s="11"/>
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="11"/>
       <c r="R22" s="11"/>
       <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
+      <c r="T22" s="11">
+        <v>272</v>
+      </c>
+      <c r="U22" s="11">
+        <v>0</v>
+      </c>
+      <c r="V22" s="11">
+        <v>273</v>
+      </c>
+      <c r="W22" s="11">
+        <v>0</v>
+      </c>
       <c r="X22" s="11"/>
       <c r="Y22" s="11"/>
       <c r="Z22" s="11"/>
@@ -3222,82 +3216,85 @@
     </row>
     <row r="23" spans="2:81">
       <c r="B23" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="14">
-        <f t="shared" ref="C23:F23" si="17">+C21/C24</f>
-        <v>0.29333628514500776</v>
-      </c>
-      <c r="D23" s="14">
-        <f t="shared" si="17"/>
-        <v>0.45662002152852532</v>
-      </c>
-      <c r="E23" s="14">
-        <f t="shared" si="17"/>
-        <v>-0.40210165129744802</v>
-      </c>
-      <c r="F23" s="14" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G23" s="14">
-        <f>+G21/G24</f>
-        <v>1.1720979765708199</v>
-      </c>
-      <c r="H23" s="14">
-        <f t="shared" ref="H23:L23" si="18">+H21/H24</f>
-        <v>1.0548119821542383</v>
-      </c>
-      <c r="I23" s="14">
-        <f t="shared" si="18"/>
-        <v>0.87823504454815449</v>
-      </c>
-      <c r="J23" s="14" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K23" s="14">
-        <f t="shared" si="18"/>
-        <v>1.5500949166842439</v>
-      </c>
-      <c r="L23" s="14">
-        <f t="shared" si="18"/>
-        <v>1.9779052475037178</v>
-      </c>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
+        <v>38</v>
+      </c>
+      <c r="C23" s="11">
+        <f t="shared" ref="C23:F23" si="13">+C21-C22</f>
+        <v>1325</v>
+      </c>
+      <c r="D23" s="11">
+        <f t="shared" si="13"/>
+        <v>2121</v>
+      </c>
+      <c r="E23" s="11">
+        <f t="shared" si="13"/>
+        <v>-1875</v>
+      </c>
+      <c r="F23" s="11">
+        <f t="shared" si="13"/>
+        <v>14054</v>
+      </c>
+      <c r="G23" s="11">
+        <f>+G21-G22</f>
+        <v>5503</v>
+      </c>
+      <c r="H23" s="11">
+        <f t="shared" ref="H23:M23" si="14">+H21-H22</f>
+        <v>4965</v>
+      </c>
+      <c r="I23" s="11">
+        <f t="shared" si="14"/>
+        <v>4140</v>
+      </c>
+      <c r="J23" s="11">
+        <f t="shared" si="14"/>
+        <v>8518</v>
+      </c>
+      <c r="K23" s="11">
+        <f t="shared" si="14"/>
+        <v>7349</v>
+      </c>
+      <c r="L23" s="11">
+        <f t="shared" si="14"/>
+        <v>9310</v>
+      </c>
+      <c r="M23" s="11">
+        <f t="shared" si="14"/>
+        <v>13088</v>
+      </c>
+      <c r="N23" s="11"/>
       <c r="O23" s="11"/>
-      <c r="P23" s="14" t="e">
-        <f t="shared" ref="P23:U23" si="19">+P21/P24</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q23" s="14" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R23" s="14" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S23" s="14" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T23" s="14">
-        <f t="shared" si="19"/>
-        <v>2.7446808510638299</v>
-      </c>
-      <c r="U23" s="14">
-        <f t="shared" si="19"/>
-        <v>3.3940708604483008</v>
-      </c>
-      <c r="V23" s="14">
-        <f>+V21/V24</f>
-        <v>1.2748702422145328</v>
-      </c>
-      <c r="W23" s="14">
-        <f>+W21/W24</f>
-        <v>4.9078947368421053</v>
+      <c r="P23" s="11">
+        <f t="shared" ref="P23:U23" si="15">+P21-P22</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="11">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="11">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="11">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="11">
+        <f t="shared" si="15"/>
+        <v>11223</v>
+      </c>
+      <c r="U23" s="11">
+        <f t="shared" si="15"/>
+        <v>14082</v>
+      </c>
+      <c r="V23" s="11">
+        <f>+V21-V22</f>
+        <v>5895</v>
+      </c>
+      <c r="W23" s="11">
+        <f t="shared" ref="W23" si="16">+W21-W22</f>
+        <v>23126</v>
       </c>
       <c r="X23" s="11"/>
       <c r="Y23" s="11"/>
@@ -3359,35 +3356,16 @@
       <c r="CC23" s="11"/>
     </row>
     <row r="24" spans="2:81">
-      <c r="B24" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="11">
-        <v>4517</v>
-      </c>
-      <c r="D24" s="11">
-        <v>4645</v>
-      </c>
-      <c r="E24" s="11">
-        <v>4663</v>
-      </c>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="11">
-        <v>4695</v>
-      </c>
-      <c r="H24" s="11">
-        <v>4707</v>
-      </c>
-      <c r="I24" s="11">
-        <v>4714</v>
-      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
       <c r="J24" s="11"/>
-      <c r="K24" s="11">
-        <v>4741</v>
-      </c>
-      <c r="L24" s="11">
-        <v>4707</v>
-      </c>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
       <c r="O24" s="11"/>
@@ -3395,18 +3373,10 @@
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
       <c r="S24" s="11"/>
-      <c r="T24" s="11">
-        <v>4089</v>
-      </c>
-      <c r="U24" s="11">
-        <v>4149</v>
-      </c>
-      <c r="V24" s="11">
-        <v>4624</v>
-      </c>
-      <c r="W24" s="11">
-        <v>4712</v>
-      </c>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
       <c r="X24" s="11"/>
       <c r="Y24" s="11"/>
       <c r="Z24" s="11"/>
@@ -3467,27 +3437,87 @@
       <c r="CC24" s="11"/>
     </row>
     <row r="25" spans="2:81">
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
+      <c r="B25" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="14">
+        <f t="shared" ref="C25:F25" si="17">+C23/C26</f>
+        <v>0.29333628514500776</v>
+      </c>
+      <c r="D25" s="14">
+        <f t="shared" si="17"/>
+        <v>0.45662002152852532</v>
+      </c>
+      <c r="E25" s="14">
+        <f t="shared" si="17"/>
+        <v>-0.40210165129744802</v>
+      </c>
+      <c r="F25" s="14" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="14">
+        <f>+G23/G26</f>
+        <v>1.1720979765708199</v>
+      </c>
+      <c r="H25" s="14">
+        <f t="shared" ref="H25:M25" si="18">+H23/H26</f>
+        <v>1.0548119821542383</v>
+      </c>
+      <c r="I25" s="14">
+        <f t="shared" si="18"/>
+        <v>0.87823504454815449</v>
+      </c>
+      <c r="J25" s="14" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K25" s="14">
+        <f t="shared" si="18"/>
+        <v>1.5500949166842439</v>
+      </c>
+      <c r="L25" s="14">
+        <f t="shared" si="18"/>
+        <v>1.9779052475037178</v>
+      </c>
+      <c r="M25" s="14">
+        <f t="shared" si="18"/>
+        <v>2.746118338229123</v>
+      </c>
+      <c r="N25" s="14"/>
       <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="11"/>
-      <c r="W25" s="11"/>
+      <c r="P25" s="14" t="e">
+        <f t="shared" ref="P25:U25" si="19">+P23/P26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q25" s="14" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R25" s="14" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S25" s="14" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T25" s="14">
+        <f t="shared" si="19"/>
+        <v>2.7446808510638299</v>
+      </c>
+      <c r="U25" s="14">
+        <f t="shared" si="19"/>
+        <v>3.3940708604483008</v>
+      </c>
+      <c r="V25" s="14">
+        <f>+V23/V26</f>
+        <v>1.2748702422145328</v>
+      </c>
+      <c r="W25" s="14">
+        <f>+W23/W26</f>
+        <v>4.9078947368421053</v>
+      </c>
       <c r="X25" s="11"/>
       <c r="Y25" s="11"/>
       <c r="Z25" s="11"/>
@@ -3549,67 +3579,54 @@
     </row>
     <row r="26" spans="2:81">
       <c r="B26" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
+        <v>4</v>
+      </c>
+      <c r="C26" s="11">
+        <v>4517</v>
+      </c>
+      <c r="D26" s="11">
+        <v>4645</v>
+      </c>
+      <c r="E26" s="11">
+        <v>4663</v>
+      </c>
       <c r="F26" s="11"/>
-      <c r="G26" s="15">
-        <f t="shared" ref="G26:G27" si="20">+G3/C3-1</f>
-        <v>0.10240151106314088</v>
-      </c>
-      <c r="H26" s="15">
-        <f t="shared" ref="H26:H28" si="21">+H3/D3-1</f>
-        <v>0.18270300333704115</v>
-      </c>
-      <c r="I26" s="15">
-        <f t="shared" ref="I26:I28" si="22">+I3/E3-1</f>
-        <v>0.24438768651700493</v>
-      </c>
-      <c r="J26" s="15" t="e">
-        <f t="shared" ref="J26:L28" si="23">+J3/F3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K26" s="15">
-        <f t="shared" si="23"/>
-        <v>0.72928650104026427</v>
-      </c>
-      <c r="L26" s="15">
-        <f t="shared" si="23"/>
-        <v>0.98589231130966382</v>
-      </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
+      <c r="G26" s="11">
+        <v>4695</v>
+      </c>
+      <c r="H26" s="11">
+        <v>4707</v>
+      </c>
+      <c r="I26" s="11">
+        <v>4714</v>
+      </c>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11">
+        <v>4741</v>
+      </c>
+      <c r="L26" s="11">
+        <v>4707</v>
+      </c>
+      <c r="M26" s="11">
+        <v>4766</v>
+      </c>
+      <c r="N26" s="11"/>
       <c r="O26" s="11"/>
       <c r="P26" s="11"/>
-      <c r="Q26" s="15" t="e">
-        <f t="shared" ref="Q26:U28" si="24">+Q3/P3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R26" s="15" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S26" s="15" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T26" s="15" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U26" s="15">
-        <f t="shared" si="24"/>
-        <v>6.1422536819271567E-2</v>
-      </c>
-      <c r="V26" s="15">
-        <f>+V3/U3-1</f>
-        <v>8.8487325660607352E-2</v>
-      </c>
-      <c r="W26" s="15">
-        <f>+W3/V3-1</f>
-        <v>0.47722256991337009</v>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
+      <c r="T26" s="11">
+        <v>4089</v>
+      </c>
+      <c r="U26" s="11">
+        <v>4149</v>
+      </c>
+      <c r="V26" s="11">
+        <v>4624</v>
+      </c>
+      <c r="W26" s="11">
+        <v>4712</v>
       </c>
       <c r="X26" s="11"/>
       <c r="Y26" s="11"/>
@@ -3671,69 +3688,27 @@
       <c r="CC26" s="11"/>
     </row>
     <row r="27" spans="2:81">
-      <c r="B27" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="15">
-        <f t="shared" si="20"/>
-        <v>0.48274346010112112</v>
-      </c>
-      <c r="H27" s="15">
-        <f t="shared" si="21"/>
-        <v>0.2271954674220964</v>
-      </c>
-      <c r="I27" s="15">
-        <f t="shared" si="22"/>
-        <v>0.18853186579087522</v>
-      </c>
-      <c r="J27" s="15" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K27" s="15">
-        <f t="shared" si="23"/>
-        <v>-0.38013343217197926</v>
-      </c>
-      <c r="L27" s="15">
-        <f t="shared" si="23"/>
-        <v>-0.18513388734995384</v>
-      </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
-      <c r="Q27" s="15" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R27" s="15" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S27" s="15" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T27" s="15" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U27" s="15">
-        <f t="shared" si="24"/>
-        <v>0.14467224949465773</v>
-      </c>
-      <c r="V27" s="15">
-        <f t="shared" ref="V27:W28" si="25">+V4/U4-1</f>
-        <v>1.6759586276488396</v>
-      </c>
-      <c r="W27" s="15">
-        <f t="shared" si="25"/>
-        <v>-0.10252180061277394</v>
-      </c>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="11"/>
+      <c r="V27" s="11"/>
+      <c r="W27" s="11"/>
       <c r="X27" s="11"/>
       <c r="Y27" s="11"/>
       <c r="Z27" s="11"/>
@@ -3794,74 +3769,77 @@
       <c r="CC27" s="11"/>
     </row>
     <row r="28" spans="2:81">
-      <c r="B28" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="16">
-        <f>+G5/C5-1</f>
-        <v>0.24705292199648854</v>
-      </c>
-      <c r="H28" s="16">
-        <f t="shared" si="21"/>
-        <v>0.20156963241771453</v>
-      </c>
-      <c r="I28" s="16">
-        <f t="shared" si="22"/>
-        <v>0.2203182374541004</v>
-      </c>
-      <c r="J28" s="16">
+      <c r="B28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="15">
+        <f t="shared" ref="G28:G29" si="20">+G5/C5-1</f>
+        <v>0.10240151106314088</v>
+      </c>
+      <c r="H28" s="15">
+        <f t="shared" ref="H28:H30" si="21">+H5/D5-1</f>
+        <v>0.18270300333704115</v>
+      </c>
+      <c r="I28" s="15">
+        <f t="shared" ref="I28:I30" si="22">+I5/E5-1</f>
+        <v>0.24438768651700493</v>
+      </c>
+      <c r="J28" s="15" t="e">
+        <f t="shared" ref="J28:M30" si="23">+J5/F5-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K28" s="15">
         <f t="shared" si="23"/>
-        <v>0.2818414686210331</v>
-      </c>
-      <c r="K28" s="16">
+        <v>0.72928650104026427</v>
+      </c>
+      <c r="L28" s="15">
         <f t="shared" si="23"/>
-        <v>0.29465004022526142</v>
-      </c>
-      <c r="L28" s="16">
+        <v>0.98589231130966382</v>
+      </c>
+      <c r="M28" s="15">
         <f t="shared" si="23"/>
-        <v>0.47873900293255134</v>
-      </c>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="16" t="e">
+        <v>-1</v>
+      </c>
+      <c r="N28" s="15"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="15" t="e">
+        <f t="shared" ref="Q28:U30" si="24">+Q5/P5-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R28" s="15" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R28" s="16" t="e">
+      <c r="S28" s="15" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S28" s="16" t="e">
+      <c r="T28" s="15" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T28" s="16" t="e">
+      <c r="U28" s="15">
         <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U28" s="16">
-        <f t="shared" si="24"/>
-        <v>7.8788061319760239E-2</v>
-      </c>
-      <c r="V28" s="16">
-        <f t="shared" si="25"/>
-        <v>0.43985035874815037</v>
-      </c>
-      <c r="W28" s="16">
-        <f t="shared" si="25"/>
-        <v>0.23874432853763516</v>
-      </c>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="13"/>
-      <c r="AA28" s="13"/>
-      <c r="AB28" s="13"/>
+        <v>6.1422536819271567E-2</v>
+      </c>
+      <c r="V28" s="15">
+        <f>+V5/U5-1</f>
+        <v>8.8487325660607352E-2</v>
+      </c>
+      <c r="W28" s="15">
+        <f>+W5/V5-1</f>
+        <v>0.47722256991337009</v>
+      </c>
+      <c r="X28" s="11"/>
+      <c r="Y28" s="11"/>
+      <c r="Z28" s="11"/>
+      <c r="AA28" s="11"/>
+      <c r="AB28" s="11"/>
       <c r="AC28" s="11"/>
       <c r="AD28" s="11"/>
       <c r="AE28" s="11"/>
@@ -3918,82 +3896,70 @@
     </row>
     <row r="29" spans="2:81">
       <c r="B29" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="15">
-        <f t="shared" ref="C29:G29" si="26">+C9/C5</f>
-        <v>0.61658724186940894</v>
-      </c>
-      <c r="D29" s="15">
-        <f t="shared" si="26"/>
-        <v>0.62272763674221188</v>
-      </c>
-      <c r="E29" s="15">
-        <f t="shared" si="26"/>
-        <v>0.6392288861689106</v>
-      </c>
-      <c r="F29" s="15">
-        <f t="shared" si="26"/>
-        <v>1</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="15">
-        <f t="shared" si="26"/>
-        <v>0.68014212925717354</v>
+        <f t="shared" si="20"/>
+        <v>0.48274346010112112</v>
       </c>
       <c r="H29" s="15">
-        <f t="shared" ref="H29:I29" si="27">+H9/H5</f>
-        <v>0.6796187683284457</v>
+        <f t="shared" si="21"/>
+        <v>0.2271954674220964</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" si="27"/>
-        <v>0.67095035105315948</v>
-      </c>
-      <c r="J29" s="15">
-        <f>+J9/J5</f>
-        <v>0.6799333888426311</v>
+        <f t="shared" si="22"/>
+        <v>0.18853186579087522</v>
+      </c>
+      <c r="J29" s="15" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="K29" s="15">
-        <f>+K9/K5</f>
-        <v>0.68132152659106204</v>
+        <f t="shared" si="23"/>
+        <v>-0.38013343217197926</v>
       </c>
       <c r="L29" s="15">
-        <f>+L9/L5</f>
-        <v>0.69477622030919006</v>
-      </c>
-      <c r="M29" s="15"/>
+        <f t="shared" si="23"/>
+        <v>-0.18513388734995384</v>
+      </c>
+      <c r="M29" s="15">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
       <c r="N29" s="15"/>
       <c r="O29" s="11"/>
-      <c r="P29" s="15" t="e">
-        <f t="shared" ref="P29:U29" si="28">+P9/P5</f>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q29" s="15" t="e">
-        <f t="shared" si="28"/>
+      <c r="R29" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R29" s="15" t="e">
-        <f t="shared" si="28"/>
+      <c r="S29" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S29" s="15" t="e">
-        <f t="shared" si="28"/>
+      <c r="T29" s="15" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T29" s="15">
-        <f t="shared" si="28"/>
-        <v>0.66545191699545225</v>
-      </c>
       <c r="U29" s="15">
-        <f t="shared" si="28"/>
-        <v>0.68929897540411511</v>
+        <f t="shared" si="24"/>
+        <v>0.14467224949465773</v>
       </c>
       <c r="V29" s="15">
-        <f>+V9/V5</f>
-        <v>0.63033699150734868</v>
+        <f t="shared" ref="V29:W30" si="25">+V6/U6-1</f>
+        <v>1.6759586276488396</v>
       </c>
       <c r="W29" s="15">
-        <f>+W9/W5</f>
-        <v>0.67766525271181932</v>
+        <f t="shared" si="25"/>
+        <v>-0.10252180061277394</v>
       </c>
       <c r="X29" s="11"/>
       <c r="Y29" s="11"/>
@@ -4055,89 +4021,77 @@
       <c r="CC29" s="11"/>
     </row>
     <row r="30" spans="2:81">
-      <c r="B30" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="15">
-        <f t="shared" ref="C30:G30" si="29">+C14/C5</f>
-        <v>0.17414931861884458</v>
-      </c>
-      <c r="D30" s="15">
-        <f t="shared" si="29"/>
-        <v>0.23744694482261552</v>
-      </c>
-      <c r="E30" s="15">
-        <f t="shared" si="29"/>
-        <v>0.28977968176254593</v>
-      </c>
-      <c r="F30" s="15">
-        <f t="shared" si="29"/>
-        <v>1</v>
-      </c>
-      <c r="G30" s="15">
-        <f t="shared" si="29"/>
-        <v>0.41968356127648165</v>
-      </c>
-      <c r="H30" s="15">
-        <f t="shared" ref="H30:I30" si="30">+H14/H5</f>
-        <v>0.38849640095974408</v>
-      </c>
-      <c r="I30" s="15">
-        <f t="shared" si="30"/>
-        <v>0.36904463390170511</v>
-      </c>
-      <c r="J30" s="15">
-        <f>+J14/J5</f>
-        <v>0.41676380793782958</v>
-      </c>
-      <c r="K30" s="15">
-        <f>+K14/K5</f>
-        <v>0.44342602661695407</v>
-      </c>
-      <c r="L30" s="15">
-        <f>+L14/L5</f>
-        <v>0.48623067562085909</v>
-      </c>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="15" t="e">
-        <f t="shared" ref="P30:U30" si="31">+P14/P5</f>
+      <c r="B30" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="16">
+        <f>+G7/C7-1</f>
+        <v>0.24705292199648854</v>
+      </c>
+      <c r="H30" s="16">
+        <f t="shared" si="21"/>
+        <v>0.20156963241771453</v>
+      </c>
+      <c r="I30" s="16">
+        <f t="shared" si="22"/>
+        <v>0.2203182374541004</v>
+      </c>
+      <c r="J30" s="16">
+        <f t="shared" si="23"/>
+        <v>0.2818414686210331</v>
+      </c>
+      <c r="K30" s="16">
+        <f t="shared" si="23"/>
+        <v>0.29465004022526142</v>
+      </c>
+      <c r="L30" s="16">
+        <f t="shared" si="23"/>
+        <v>0.47873900293255134</v>
+      </c>
+      <c r="M30" s="16">
+        <f t="shared" si="23"/>
+        <v>0.85500250752256779</v>
+      </c>
+      <c r="N30" s="16"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="16" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q30" s="15" t="e">
-        <f t="shared" si="31"/>
+      <c r="R30" s="16" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R30" s="15" t="e">
-        <f t="shared" si="31"/>
+      <c r="S30" s="16" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S30" s="15" t="e">
-        <f t="shared" si="31"/>
+      <c r="T30" s="16" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T30" s="15">
-        <f t="shared" si="31"/>
-        <v>0.42842514230641809</v>
-      </c>
-      <c r="U30" s="15">
-        <f t="shared" si="31"/>
-        <v>0.45246935983695802</v>
-      </c>
-      <c r="V30" s="15">
-        <f>+V14/V5</f>
-        <v>0.26104238569822003</v>
-      </c>
-      <c r="W30" s="15">
-        <f>+W14/W5</f>
-        <v>0.39889179332258518</v>
-      </c>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="11"/>
-      <c r="Z30" s="11"/>
-      <c r="AA30" s="11"/>
-      <c r="AB30" s="11"/>
+      <c r="U30" s="16">
+        <f t="shared" si="24"/>
+        <v>7.8788061319760239E-2</v>
+      </c>
+      <c r="V30" s="16">
+        <f t="shared" si="25"/>
+        <v>0.43985035874815037</v>
+      </c>
+      <c r="W30" s="16">
+        <f t="shared" si="25"/>
+        <v>0.23874432853763516</v>
+      </c>
+      <c r="X30" s="13"/>
+      <c r="Y30" s="13"/>
+      <c r="Z30" s="13"/>
+      <c r="AA30" s="13"/>
+      <c r="AB30" s="13"/>
       <c r="AC30" s="11"/>
       <c r="AD30" s="11"/>
       <c r="AE30" s="11"/>
@@ -4194,82 +4148,85 @@
     </row>
     <row r="31" spans="2:81">
       <c r="B31" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C31" s="15">
-        <f t="shared" ref="C31:G31" si="32">+C18/C17</f>
-        <v>4.8815506101938265E-2</v>
+        <f t="shared" ref="C31:G31" si="26">+C11/C7</f>
+        <v>0.61658724186940894</v>
       </c>
       <c r="D31" s="15">
-        <f t="shared" si="32"/>
-        <v>-5.7855361596009978E-2</v>
+        <f t="shared" si="26"/>
+        <v>0.62272763674221188</v>
       </c>
       <c r="E31" s="15">
-        <f t="shared" si="32"/>
-        <v>1.5103349964362081</v>
+        <f t="shared" si="26"/>
+        <v>0.6392288861689106</v>
       </c>
       <c r="F31" s="15">
-        <f t="shared" si="32"/>
-        <v>0</v>
+        <f t="shared" si="26"/>
+        <v>1</v>
       </c>
       <c r="G31" s="15">
-        <f t="shared" si="32"/>
-        <v>-2.3679417122040073E-3</v>
+        <f t="shared" si="26"/>
+        <v>0.68014212925717354</v>
       </c>
       <c r="H31" s="15">
-        <f t="shared" ref="H31:I31" si="33">+H18/H17</f>
-        <v>2.359882005899705E-2</v>
+        <f t="shared" ref="H31:I31" si="27">+H11/H7</f>
+        <v>0.6796187683284457</v>
       </c>
       <c r="I31" s="15">
-        <f t="shared" si="33"/>
-        <v>0.21665089877010407</v>
+        <f t="shared" si="27"/>
+        <v>0.67095035105315948</v>
       </c>
       <c r="J31" s="15">
-        <f>+J18/J17</f>
-        <v>-0.24006405590333382</v>
+        <f>+J11/J7</f>
+        <v>0.6799333888426311</v>
       </c>
       <c r="K31" s="15">
-        <f>+K18/K17</f>
-        <v>0.10323367907260525</v>
+        <f>+K11/K7</f>
+        <v>0.68132152659106204</v>
       </c>
       <c r="L31" s="15">
-        <f>+L18/L17</f>
-        <v>8.0947680157946691E-2</v>
-      </c>
-      <c r="M31" s="15"/>
+        <f>+L11/L7</f>
+        <v>0.69477622030919006</v>
+      </c>
+      <c r="M31" s="15">
+        <f>+M11/M7</f>
+        <v>0.69129127099455911</v>
+      </c>
       <c r="N31" s="15"/>
       <c r="O31" s="11"/>
       <c r="P31" s="15" t="e">
-        <f t="shared" ref="P31:U31" si="34">+P18/P17</f>
+        <f t="shared" ref="P31:U31" si="28">+P11/P7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q31" s="15" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R31" s="15" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S31" s="15" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T31" s="15">
-        <f t="shared" si="34"/>
-        <v>7.5518738941611707E-2</v>
+        <f t="shared" si="28"/>
+        <v>0.66545191699545225</v>
       </c>
       <c r="U31" s="15">
-        <f t="shared" si="34"/>
-        <v>6.7231900377558454E-2</v>
+        <f t="shared" si="28"/>
+        <v>0.68929897540411511</v>
       </c>
       <c r="V31" s="15">
-        <f>+V18/V17</f>
-        <v>0.37797498991528844</v>
+        <f>+V11/V7</f>
+        <v>0.63033699150734868</v>
       </c>
       <c r="W31" s="15">
-        <f>+W18/W17</f>
-        <v>-1.7466672532887501E-2</v>
+        <f>+W11/W7</f>
+        <v>0.67766525271181932</v>
       </c>
       <c r="X31" s="11"/>
       <c r="Y31" s="11"/>
@@ -4331,27 +4288,87 @@
       <c r="CC31" s="11"/>
     </row>
     <row r="32" spans="2:81">
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
+      <c r="B32" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="15">
+        <f t="shared" ref="C32:G32" si="29">+C16/C7</f>
+        <v>0.17414931861884458</v>
+      </c>
+      <c r="D32" s="15">
+        <f t="shared" si="29"/>
+        <v>0.23744694482261552</v>
+      </c>
+      <c r="E32" s="15">
+        <f t="shared" si="29"/>
+        <v>0.28977968176254593</v>
+      </c>
+      <c r="F32" s="15">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G32" s="15">
+        <f t="shared" si="29"/>
+        <v>0.41968356127648165</v>
+      </c>
+      <c r="H32" s="15">
+        <f t="shared" ref="H32:I32" si="30">+H16/H7</f>
+        <v>0.38849640095974408</v>
+      </c>
+      <c r="I32" s="15">
+        <f t="shared" si="30"/>
+        <v>0.36904463390170511</v>
+      </c>
+      <c r="J32" s="15">
+        <f>+J16/J7</f>
+        <v>0.41676380793782958</v>
+      </c>
+      <c r="K32" s="15">
+        <f>+K16/K7</f>
+        <v>0.44342602661695407</v>
+      </c>
+      <c r="L32" s="15">
+        <f>+L16/L7</f>
+        <v>0.48623067562085909</v>
+      </c>
+      <c r="M32" s="15">
+        <f>+M16/M7</f>
+        <v>0.53918421141563311</v>
+      </c>
+      <c r="N32" s="15"/>
       <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
-      <c r="R32" s="11"/>
-      <c r="S32" s="11"/>
-      <c r="T32" s="11"/>
-      <c r="U32" s="11"/>
-      <c r="V32" s="11"/>
-      <c r="W32" s="11"/>
+      <c r="P32" s="15" t="e">
+        <f t="shared" ref="P32:U32" si="31">+P16/P7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q32" s="15" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R32" s="15" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S32" s="15" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T32" s="15">
+        <f t="shared" si="31"/>
+        <v>0.42842514230641809</v>
+      </c>
+      <c r="U32" s="15">
+        <f t="shared" si="31"/>
+        <v>0.45246935983695802</v>
+      </c>
+      <c r="V32" s="15">
+        <f>+V16/V7</f>
+        <v>0.26104238569822003</v>
+      </c>
+      <c r="W32" s="15">
+        <f>+W16/W7</f>
+        <v>0.39889179332258518</v>
+      </c>
       <c r="X32" s="11"/>
       <c r="Y32" s="11"/>
       <c r="Z32" s="11"/>
@@ -4411,28 +4428,88 @@
       <c r="CB32" s="11"/>
       <c r="CC32" s="11"/>
     </row>
-    <row r="33" spans="3:81">
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
+    <row r="33" spans="2:81">
+      <c r="B33" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="15">
+        <f t="shared" ref="C33:G33" si="32">+C20/C19</f>
+        <v>4.8815506101938265E-2</v>
+      </c>
+      <c r="D33" s="15">
+        <f t="shared" si="32"/>
+        <v>-5.7855361596009978E-2</v>
+      </c>
+      <c r="E33" s="15">
+        <f t="shared" si="32"/>
+        <v>1.5103349964362081</v>
+      </c>
+      <c r="F33" s="15">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="15">
+        <f t="shared" si="32"/>
+        <v>-2.3679417122040073E-3</v>
+      </c>
+      <c r="H33" s="15">
+        <f t="shared" ref="H33:I33" si="33">+H20/H19</f>
+        <v>2.359882005899705E-2</v>
+      </c>
+      <c r="I33" s="15">
+        <f t="shared" si="33"/>
+        <v>0.21665089877010407</v>
+      </c>
+      <c r="J33" s="15">
+        <f>+J20/J19</f>
+        <v>-0.24006405590333382</v>
+      </c>
+      <c r="K33" s="15">
+        <f>+K20/K19</f>
+        <v>0.10323367907260525</v>
+      </c>
+      <c r="L33" s="15">
+        <f>+L20/L19</f>
+        <v>8.0947680157946691E-2</v>
+      </c>
+      <c r="M33" s="15">
+        <f>+M20/M19</f>
+        <v>0.14317512274959082</v>
+      </c>
+      <c r="N33" s="15"/>
       <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
-      <c r="R33" s="11"/>
-      <c r="S33" s="11"/>
-      <c r="T33" s="11"/>
-      <c r="U33" s="11"/>
-      <c r="V33" s="11"/>
-      <c r="W33" s="11"/>
+      <c r="P33" s="15" t="e">
+        <f t="shared" ref="P33:U33" si="34">+P20/P19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q33" s="15" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R33" s="15" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S33" s="15" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T33" s="15">
+        <f t="shared" si="34"/>
+        <v>7.5518738941611707E-2</v>
+      </c>
+      <c r="U33" s="15">
+        <f t="shared" si="34"/>
+        <v>6.7231900377558454E-2</v>
+      </c>
+      <c r="V33" s="15">
+        <f>+V20/V19</f>
+        <v>0.37797498991528844</v>
+      </c>
+      <c r="W33" s="15">
+        <f>+W20/W19</f>
+        <v>-1.7466672532887501E-2</v>
+      </c>
       <c r="X33" s="11"/>
       <c r="Y33" s="11"/>
       <c r="Z33" s="11"/>
@@ -4492,7 +4569,7 @@
       <c r="CB33" s="11"/>
       <c r="CC33" s="11"/>
     </row>
-    <row r="34" spans="3:81">
+    <row r="34" spans="2:81">
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
@@ -4573,7 +4650,7 @@
       <c r="CB34" s="11"/>
       <c r="CC34" s="11"/>
     </row>
-    <row r="35" spans="3:81">
+    <row r="35" spans="2:81">
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
@@ -4654,7 +4731,7 @@
       <c r="CB35" s="11"/>
       <c r="CC35" s="11"/>
     </row>
-    <row r="36" spans="3:81">
+    <row r="36" spans="2:81">
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -4735,7 +4812,7 @@
       <c r="CB36" s="11"/>
       <c r="CC36" s="11"/>
     </row>
-    <row r="37" spans="3:81">
+    <row r="37" spans="2:81">
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -4816,7 +4893,7 @@
       <c r="CB37" s="11"/>
       <c r="CC37" s="11"/>
     </row>
-    <row r="38" spans="3:81">
+    <row r="38" spans="2:81">
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -4897,7 +4974,7 @@
       <c r="CB38" s="11"/>
       <c r="CC38" s="11"/>
     </row>
-    <row r="39" spans="3:81">
+    <row r="39" spans="2:81">
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
@@ -4978,7 +5055,7 @@
       <c r="CB39" s="11"/>
       <c r="CC39" s="11"/>
     </row>
-    <row r="40" spans="3:81">
+    <row r="40" spans="2:81">
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
@@ -5059,7 +5136,7 @@
       <c r="CB40" s="11"/>
       <c r="CC40" s="11"/>
     </row>
-    <row r="41" spans="3:81">
+    <row r="41" spans="2:81">
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
@@ -5140,7 +5217,7 @@
       <c r="CB41" s="11"/>
       <c r="CC41" s="11"/>
     </row>
-    <row r="42" spans="3:81">
+    <row r="42" spans="2:81">
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -5221,7 +5298,7 @@
       <c r="CB42" s="11"/>
       <c r="CC42" s="11"/>
     </row>
-    <row r="43" spans="3:81">
+    <row r="43" spans="2:81">
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
@@ -5302,7 +5379,7 @@
       <c r="CB43" s="11"/>
       <c r="CC43" s="11"/>
     </row>
-    <row r="44" spans="3:81">
+    <row r="44" spans="2:81">
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -5383,7 +5460,7 @@
       <c r="CB44" s="11"/>
       <c r="CC44" s="11"/>
     </row>
-    <row r="45" spans="3:81">
+    <row r="45" spans="2:81">
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
@@ -5464,7 +5541,7 @@
       <c r="CB45" s="11"/>
       <c r="CC45" s="11"/>
     </row>
-    <row r="46" spans="3:81">
+    <row r="46" spans="2:81">
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
@@ -5545,7 +5622,7 @@
       <c r="CB46" s="11"/>
       <c r="CC46" s="11"/>
     </row>
-    <row r="47" spans="3:81">
+    <row r="47" spans="2:81">
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
       <c r="E47" s="11"/>
@@ -5626,7 +5703,7 @@
       <c r="CB47" s="11"/>
       <c r="CC47" s="11"/>
     </row>
-    <row r="48" spans="3:81">
+    <row r="48" spans="2:81">
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
       <c r="E48" s="11"/>
@@ -37702,6 +37779,168 @@
       <c r="CB443" s="11"/>
       <c r="CC443" s="11"/>
     </row>
+    <row r="444" spans="3:81">
+      <c r="C444" s="11"/>
+      <c r="D444" s="11"/>
+      <c r="E444" s="11"/>
+      <c r="F444" s="11"/>
+      <c r="G444" s="11"/>
+      <c r="H444" s="11"/>
+      <c r="I444" s="11"/>
+      <c r="J444" s="11"/>
+      <c r="K444" s="11"/>
+      <c r="L444" s="11"/>
+      <c r="M444" s="11"/>
+      <c r="N444" s="11"/>
+      <c r="O444" s="11"/>
+      <c r="P444" s="11"/>
+      <c r="Q444" s="11"/>
+      <c r="R444" s="11"/>
+      <c r="S444" s="11"/>
+      <c r="T444" s="11"/>
+      <c r="U444" s="11"/>
+      <c r="V444" s="11"/>
+      <c r="W444" s="11"/>
+      <c r="X444" s="11"/>
+      <c r="Y444" s="11"/>
+      <c r="Z444" s="11"/>
+      <c r="AA444" s="11"/>
+      <c r="AB444" s="11"/>
+      <c r="AC444" s="11"/>
+      <c r="AD444" s="11"/>
+      <c r="AE444" s="11"/>
+      <c r="AF444" s="11"/>
+      <c r="AG444" s="11"/>
+      <c r="AH444" s="11"/>
+      <c r="AI444" s="11"/>
+      <c r="AJ444" s="11"/>
+      <c r="AK444" s="11"/>
+      <c r="AL444" s="11"/>
+      <c r="AM444" s="11"/>
+      <c r="AN444" s="11"/>
+      <c r="AO444" s="11"/>
+      <c r="AP444" s="11"/>
+      <c r="AQ444" s="11"/>
+      <c r="AR444" s="11"/>
+      <c r="AS444" s="11"/>
+      <c r="AT444" s="11"/>
+      <c r="AU444" s="11"/>
+      <c r="AV444" s="11"/>
+      <c r="AW444" s="11"/>
+      <c r="AX444" s="11"/>
+      <c r="AY444" s="11"/>
+      <c r="AZ444" s="11"/>
+      <c r="BA444" s="11"/>
+      <c r="BB444" s="11"/>
+      <c r="BC444" s="11"/>
+      <c r="BD444" s="11"/>
+      <c r="BE444" s="11"/>
+      <c r="BF444" s="11"/>
+      <c r="BG444" s="11"/>
+      <c r="BH444" s="11"/>
+      <c r="BI444" s="11"/>
+      <c r="BJ444" s="11"/>
+      <c r="BK444" s="11"/>
+      <c r="BL444" s="11"/>
+      <c r="BM444" s="11"/>
+      <c r="BN444" s="11"/>
+      <c r="BO444" s="11"/>
+      <c r="BP444" s="11"/>
+      <c r="BQ444" s="11"/>
+      <c r="BR444" s="11"/>
+      <c r="BS444" s="11"/>
+      <c r="BT444" s="11"/>
+      <c r="BU444" s="11"/>
+      <c r="BV444" s="11"/>
+      <c r="BW444" s="11"/>
+      <c r="BX444" s="11"/>
+      <c r="BY444" s="11"/>
+      <c r="BZ444" s="11"/>
+      <c r="CA444" s="11"/>
+      <c r="CB444" s="11"/>
+      <c r="CC444" s="11"/>
+    </row>
+    <row r="445" spans="3:81">
+      <c r="C445" s="11"/>
+      <c r="D445" s="11"/>
+      <c r="E445" s="11"/>
+      <c r="F445" s="11"/>
+      <c r="G445" s="11"/>
+      <c r="H445" s="11"/>
+      <c r="I445" s="11"/>
+      <c r="J445" s="11"/>
+      <c r="K445" s="11"/>
+      <c r="L445" s="11"/>
+      <c r="M445" s="11"/>
+      <c r="N445" s="11"/>
+      <c r="O445" s="11"/>
+      <c r="P445" s="11"/>
+      <c r="Q445" s="11"/>
+      <c r="R445" s="11"/>
+      <c r="S445" s="11"/>
+      <c r="T445" s="11"/>
+      <c r="U445" s="11"/>
+      <c r="V445" s="11"/>
+      <c r="W445" s="11"/>
+      <c r="X445" s="11"/>
+      <c r="Y445" s="11"/>
+      <c r="Z445" s="11"/>
+      <c r="AA445" s="11"/>
+      <c r="AB445" s="11"/>
+      <c r="AC445" s="11"/>
+      <c r="AD445" s="11"/>
+      <c r="AE445" s="11"/>
+      <c r="AF445" s="11"/>
+      <c r="AG445" s="11"/>
+      <c r="AH445" s="11"/>
+      <c r="AI445" s="11"/>
+      <c r="AJ445" s="11"/>
+      <c r="AK445" s="11"/>
+      <c r="AL445" s="11"/>
+      <c r="AM445" s="11"/>
+      <c r="AN445" s="11"/>
+      <c r="AO445" s="11"/>
+      <c r="AP445" s="11"/>
+      <c r="AQ445" s="11"/>
+      <c r="AR445" s="11"/>
+      <c r="AS445" s="11"/>
+      <c r="AT445" s="11"/>
+      <c r="AU445" s="11"/>
+      <c r="AV445" s="11"/>
+      <c r="AW445" s="11"/>
+      <c r="AX445" s="11"/>
+      <c r="AY445" s="11"/>
+      <c r="AZ445" s="11"/>
+      <c r="BA445" s="11"/>
+      <c r="BB445" s="11"/>
+      <c r="BC445" s="11"/>
+      <c r="BD445" s="11"/>
+      <c r="BE445" s="11"/>
+      <c r="BF445" s="11"/>
+      <c r="BG445" s="11"/>
+      <c r="BH445" s="11"/>
+      <c r="BI445" s="11"/>
+      <c r="BJ445" s="11"/>
+      <c r="BK445" s="11"/>
+      <c r="BL445" s="11"/>
+      <c r="BM445" s="11"/>
+      <c r="BN445" s="11"/>
+      <c r="BO445" s="11"/>
+      <c r="BP445" s="11"/>
+      <c r="BQ445" s="11"/>
+      <c r="BR445" s="11"/>
+      <c r="BS445" s="11"/>
+      <c r="BT445" s="11"/>
+      <c r="BU445" s="11"/>
+      <c r="BV445" s="11"/>
+      <c r="BW445" s="11"/>
+      <c r="BX445" s="11"/>
+      <c r="BY445" s="11"/>
+      <c r="BZ445" s="11"/>
+      <c r="CA445" s="11"/>
+      <c r="CB445" s="11"/>
+      <c r="CC445" s="11"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{84AAFD7D-C4A5-43AB-BA0F-87A6F76EEBDF}"/>
